--- a/compare_metrics_summary.xlsx
+++ b/compare_metrics_summary.xlsx
@@ -92,7 +92,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -137,7 +137,7 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -182,7 +182,7 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -227,7 +227,7 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -272,27 +272,21 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_4200</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>105.38666666666667</v>
+      </c>
+      <c r="H6">
+        <v>262.76666666666665</v>
+      </c>
+      <c r="I6">
+        <v>0.8853066666666666</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -301,7 +295,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_3_compare/compare_results/iddpg/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -368,7 +362,7 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -413,7 +407,7 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -458,7 +452,7 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -503,27 +497,21 @@
         <v>5</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_2750</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>88.92333333333333</v>
+      </c>
+      <c r="H11">
+        <v>319.6</v>
+      </c>
+      <c r="I11">
+        <v>0.9134626666666668</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -532,7 +520,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_4_compare/compare_results/iddpg/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -554,7 +542,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -644,7 +632,7 @@
         <v>3</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -689,7 +677,7 @@
         <v>4</v>
       </c>
       <c r="E15">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -734,27 +722,21 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_1000</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>74.05666666666667</v>
+      </c>
+      <c r="H16">
+        <v>354.4766666666667</v>
+      </c>
+      <c r="I16">
+        <v>0.9550706666666665</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -763,7 +745,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_5_compare/compare_results/iddpg/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -785,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -830,7 +812,7 @@
         <v>2</v>
       </c>
       <c r="E18">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -875,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -920,7 +902,7 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -965,7 +947,7 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1016,27 +998,21 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_4050</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>28.003333333333334</v>
+      </c>
+      <c r="H22">
+        <v>119.15333333333334</v>
+      </c>
+      <c r="I22">
+        <v>0.9783186666666666</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1045,7 +1021,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_7_compare/compare_results/iddpg/target_1/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1169,27 +1145,21 @@
         <v>4</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_3250</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>55.62</v>
+      </c>
+      <c r="H25">
+        <v>341.1933333333333</v>
+      </c>
+      <c r="I25">
+        <v>0.966164</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1198,7 +1168,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_7_compare/compare_results/iddpg/target_4/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1190,7 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1271,27 +1241,21 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_1250</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>27.496666666666666</v>
+      </c>
+      <c r="H27">
+        <v>134.44333333333333</v>
+      </c>
+      <c r="I27">
+        <v>0.975552</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1300,7 +1264,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_8_compare/compare_results/iddpg/target_1/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1286,7 @@
         <v>2</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1424,27 +1388,21 @@
         <v>4</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_150</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>46.42</v>
+      </c>
+      <c r="H30">
+        <v>207.50666666666666</v>
+      </c>
+      <c r="I30">
+        <v>0.9791479999999999</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1453,7 +1411,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_8_compare/compare_results/iddpg/target_4/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1433,7 @@
         <v>5</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1526,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1571,7 +1529,7 @@
         <v>2</v>
       </c>
       <c r="E33">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1661,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="E35">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1706,27 +1664,21 @@
         <v>5</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_1650</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>78.41</v>
+      </c>
+      <c r="H36">
+        <v>129.13333333333333</v>
+      </c>
+      <c r="I36">
+        <v>0.9559293333333331</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1735,7 +1687,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_3_compare/compare_results/maddpg_nopf/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1802,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1847,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="E39">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1892,7 +1844,7 @@
         <v>4</v>
       </c>
       <c r="E40">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1937,27 +1889,21 @@
         <v>5</v>
       </c>
       <c r="E41">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_1300</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>61.88</v>
+      </c>
+      <c r="H41">
+        <v>161.1</v>
+      </c>
+      <c r="I41">
+        <v>0.9769506666666666</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1966,7 +1912,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_4_compare/compare_results/maddpg_nopf/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2033,7 +1979,7 @@
         <v>2</v>
       </c>
       <c r="E43">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2078,7 +2024,7 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2123,7 +2069,7 @@
         <v>4</v>
       </c>
       <c r="E45">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2168,27 +2114,21 @@
         <v>5</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_4600</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>54.8</v>
+      </c>
+      <c r="H46">
+        <v>174.38666666666666</v>
+      </c>
+      <c r="I46">
+        <v>0.9855933333333333</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2197,7 +2137,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_5_compare/compare_results/maddpg_nopf/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2264,7 +2204,7 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2309,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="E49">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2354,7 +2294,7 @@
         <v>4</v>
       </c>
       <c r="E50">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2399,27 +2339,21 @@
         <v>5</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_900</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>58.193333333333335</v>
+      </c>
+      <c r="H51">
+        <v>203.61</v>
+      </c>
+      <c r="I51">
+        <v>0.9791933333333332</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2428,7 +2362,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_6_compare/compare_results/maddpg_nopf/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2454,23 +2388,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_1000</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>28.613333333333333</v>
+      </c>
+      <c r="H52">
+        <v>43.14</v>
+      </c>
+      <c r="I52">
+        <v>0.9898626666666667</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2479,7 +2407,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_7_compare/compare_results/maddpg_nopf/target_1/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2501,27 +2429,21 @@
         <v>2</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_650</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>37.72666666666667</v>
+      </c>
+      <c r="H53">
+        <v>87.44</v>
+      </c>
+      <c r="I53">
+        <v>0.9834999999999998</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2530,7 +2452,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_7_compare/compare_results/maddpg_nopf/target_2/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2474,7 @@
         <v>3</v>
       </c>
       <c r="E54">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2603,27 +2525,21 @@
         <v>4</v>
       </c>
       <c r="E55">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_900</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>47.86666666666667</v>
+      </c>
+      <c r="H55">
+        <v>174.24</v>
+      </c>
+      <c r="I55">
+        <v>0.9897293333333335</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2632,7 +2548,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_7_compare/compare_results/maddpg_nopf/target_4/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2654,27 +2570,21 @@
         <v>5</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_500</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>49.33</v>
+      </c>
+      <c r="H56">
+        <v>205.52333333333334</v>
+      </c>
+      <c r="I56">
+        <v>0.9877413333333334</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2683,7 +2593,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_7_compare/compare_results/maddpg_nopf/target_5/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2705,27 +2615,21 @@
         <v>1</v>
       </c>
       <c r="E57">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_1200</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>27.293333333333333</v>
+      </c>
+      <c r="H57">
+        <v>47.29333333333334</v>
+      </c>
+      <c r="I57">
+        <v>0.9854226666666667</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2734,7 +2638,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_8_compare/compare_results/maddpg_nopf/target_1/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2660,7 @@
         <v>2</v>
       </c>
       <c r="E58">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2858,27 +2762,21 @@
         <v>4</v>
       </c>
       <c r="E60">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>top_ep_2400</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>44.70666666666666</v>
+      </c>
+      <c r="H60">
+        <v>172.01666666666668</v>
+      </c>
+      <c r="I60">
+        <v>0.9908079999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2887,7 +2785,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t/>
+          <t>/home/wensheng/gjq_workspace/wrjjq/newnet_6_8_compare/compare_results/maddpg_nopf/target_4/results/metrics_summary.json</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2807,7 @@
         <v>5</v>
       </c>
       <c r="E61">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2978,7 +2876,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_3000, rank_02, top_ep_2900, rank_03, top_ep_4950, rank_04, top_ep_2750, rank_05, top_ep_2700, rank_06, top_ep_4850, rank_07, top_ep_2050, rank_08, top_ep_4400, rank_09, top_ep_3400, rank_10, top_ep_950</t>
+          <t>rank_01, top_ep_3000, rank_02, top_ep_2900, rank_03, top_ep_4950, rank_04, top_ep_2750, rank_05, top_ep_2700, rank_06, top_ep_4850, rank_07, top_ep_2050, rank_08, top_ep_4400, rank_09, top_ep_3400, rank_10, top_ep_950, episode_3000, episode_2900, episode_4950, episode_2750, episode_2700, episode_4850, episode_2050, episode_4400, episode_3400, episode_950</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3023,7 +2921,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_700, rank_02, top_ep_1150, rank_03, top_ep_2400, rank_04, top_ep_1450, rank_05, top_ep_1600, rank_06, top_ep_600, rank_07, top_ep_2950, rank_08, top_ep_4850, rank_09, top_ep_850, rank_10, top_ep_1500</t>
+          <t>rank_01, top_ep_700, rank_02, top_ep_1150, rank_03, top_ep_2400, rank_04, top_ep_1450, rank_05, top_ep_1600, rank_06, top_ep_600, rank_07, top_ep_2950, rank_08, top_ep_4850, rank_09, top_ep_850, rank_10, top_ep_1500, episode_700, episode_1150, episode_2400, episode_1450, episode_1600, episode_600, episode_2950, episode_4850, episode_850, episode_1500</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3068,7 +2966,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_1950, rank_02, top_ep_1850, rank_03, top_ep_300, rank_04, top_ep_1450, rank_05, top_ep_1050, rank_06, top_ep_4300, rank_07, top_ep_2100, rank_08, top_ep_1900, rank_09, top_ep_3550, rank_10, top_ep_3900</t>
+          <t>rank_01, top_ep_1950, rank_02, top_ep_1850, rank_03, top_ep_300, rank_04, top_ep_1450, rank_05, top_ep_1050, rank_06, top_ep_4300, rank_07, top_ep_2100, rank_08, top_ep_1900, rank_09, top_ep_3550, rank_10, top_ep_3900, episode_1950, episode_1850, episode_300, episode_1450, episode_1050, episode_4300, episode_2100, episode_1900, episode_3550, episode_3900</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3113,7 +3011,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_4750, rank_02, top_ep_1700, rank_03, top_ep_1450, rank_04, top_ep_950, rank_05, top_ep_1250, rank_06, top_ep_1500, rank_07, top_ep_2000, rank_08, top_ep_850, rank_09, top_ep_1400, rank_10, top_ep_4650</t>
+          <t>rank_01, top_ep_4750, rank_02, top_ep_1700, rank_03, top_ep_1450, rank_04, top_ep_950, rank_05, top_ep_1250, rank_06, top_ep_1500, rank_07, top_ep_2000, rank_08, top_ep_850, rank_09, top_ep_1400, rank_10, top_ep_4650, episode_4750, episode_1700, episode_1450, episode_950, episode_1250, episode_1500, episode_2000, episode_850, episode_1400, episode_4650</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3209,7 +3107,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_2900, rank_02, top_ep_600, rank_03, top_ep_300, rank_04, top_ep_3650, rank_05, top_ep_4250, rank_06, top_ep_5000, rank_07, top_ep_4750, rank_08, top_ep_2200, rank_09, top_ep_2300, rank_10, top_ep_3150</t>
+          <t>rank_01, top_ep_2900, rank_02, top_ep_600, rank_03, top_ep_300, rank_04, top_ep_3650, rank_05, top_ep_4250, rank_06, top_ep_5000, rank_07, top_ep_4750, rank_08, top_ep_2200, rank_09, top_ep_2300, rank_10, top_ep_3150, episode_2900, episode_600, episode_300, episode_3650, episode_4250, episode_5000, episode_4750, episode_2200, episode_2300, episode_3150</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3254,7 +3152,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_1300, rank_02, top_ep_1200, rank_03, top_ep_1250, rank_04, top_ep_1500, rank_05, top_ep_2650, rank_06, top_ep_2550, rank_07, top_ep_2050, rank_08, top_ep_900, rank_09, top_ep_1400, rank_10, top_ep_1800</t>
+          <t>rank_01, top_ep_1300, rank_02, top_ep_1200, rank_03, top_ep_1250, rank_04, top_ep_1500, rank_05, top_ep_2650, rank_06, top_ep_2550, rank_07, top_ep_2050, rank_08, top_ep_900, rank_09, top_ep_1400, rank_10, top_ep_1800, episode_1300, episode_1200, episode_1250, episode_1500, episode_2650, episode_2550, episode_2050, episode_900, episode_1400, episode_1800</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3299,7 +3197,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_4100, rank_02, top_ep_3450, rank_03, top_ep_1150, rank_04, top_ep_3850, rank_05, top_ep_250, rank_06, top_ep_3600, rank_07, top_ep_4750, rank_08, top_ep_4150, rank_09, top_ep_900, rank_10, top_ep_650</t>
+          <t>rank_01, top_ep_4100, rank_02, top_ep_3450, rank_03, top_ep_1150, rank_04, top_ep_3850, rank_05, top_ep_250, rank_06, top_ep_3600, rank_07, top_ep_4750, rank_08, top_ep_4150, rank_09, top_ep_900, rank_10, top_ep_650, episode_4100, episode_3450, episode_1150, episode_3850, episode_250, episode_3600, episode_4750, episode_4150, episode_900, episode_650</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3344,7 +3242,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_3250, rank_02, top_ep_3900, rank_03, top_ep_2150, rank_04, top_ep_900, rank_05, top_ep_5000, rank_06, top_ep_2250, rank_07, top_ep_2100, rank_08, top_ep_1650, rank_09, top_ep_3850, rank_10, top_ep_300</t>
+          <t>rank_01, top_ep_3250, rank_02, top_ep_3900, rank_03, top_ep_2150, rank_04, top_ep_900, rank_05, top_ep_5000, rank_06, top_ep_2250, rank_07, top_ep_2100, rank_08, top_ep_1650, rank_09, top_ep_3850, rank_10, top_ep_300, episode_3250, episode_3900, episode_2150, episode_900, episode_5000, episode_2250, episode_2100, episode_1650, episode_3850, episode_300</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3440,7 +3338,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_3500, rank_02, top_ep_3000, rank_03, top_ep_3400, rank_04, top_ep_1150, rank_05, top_ep_3700, rank_06, top_ep_3750, rank_07, top_ep_2300, rank_08, top_ep_3950, rank_09, top_ep_2850, rank_10, top_ep_2750</t>
+          <t>rank_01, top_ep_3500, rank_02, top_ep_3000, rank_03, top_ep_3400, rank_04, top_ep_1150, rank_05, top_ep_3700, rank_06, top_ep_3750, rank_07, top_ep_2300, rank_08, top_ep_3950, rank_09, top_ep_2850, rank_10, top_ep_2750, episode_3500, episode_3000, episode_3400, episode_1150, episode_3700, episode_3750, episode_2300, episode_3950, episode_2850, episode_2750</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -3485,7 +3383,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_1400, rank_02, top_ep_2150, rank_03, top_ep_950, rank_04, top_ep_1650, rank_05, top_ep_1600, rank_06, top_ep_900, rank_07, top_ep_1100, rank_08, top_ep_2950, rank_09, top_ep_1000, rank_10, top_ep_1300</t>
+          <t>rank_01, top_ep_1400, rank_02, top_ep_2150, rank_03, top_ep_950, rank_04, top_ep_1650, rank_05, top_ep_1600, rank_06, top_ep_900, rank_07, top_ep_1100, rank_08, top_ep_2950, rank_09, top_ep_1000, rank_10, top_ep_1300, episode_1400, episode_2150, episode_950, episode_1650, episode_1600, episode_900, episode_1100, episode_2950, episode_1000, episode_1300</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3530,7 +3428,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_1600, rank_02, top_ep_1650, rank_03, top_ep_750, rank_04, top_ep_600, rank_05, top_ep_1500, rank_06, top_ep_1750, rank_07, top_ep_800, rank_08, top_ep_200, rank_09, top_ep_1000, rank_10, top_ep_1050</t>
+          <t>rank_01, top_ep_1600, rank_02, top_ep_1650, rank_03, top_ep_750, rank_04, top_ep_600, rank_05, top_ep_1500, rank_06, top_ep_1750, rank_07, top_ep_800, rank_08, top_ep_200, rank_09, top_ep_1000, rank_10, top_ep_1050, episode_1600, episode_1650, episode_750, episode_600, episode_1500, episode_1750, episode_800, episode_200, episode_1000, episode_1050</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3575,7 +3473,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_700, rank_02, top_ep_900, rank_03, top_ep_750, rank_04, top_ep_4550, rank_05, top_ep_300, rank_06, top_ep_600, rank_07, top_ep_2550, rank_08, top_ep_950, rank_09, top_ep_1300, rank_10, top_ep_3900</t>
+          <t>rank_01, top_ep_700, rank_02, top_ep_900, rank_03, top_ep_750, rank_04, top_ep_4550, rank_05, top_ep_300, rank_06, top_ep_600, rank_07, top_ep_2550, rank_08, top_ep_950, rank_09, top_ep_1300, rank_10, top_ep_3900, episode_700, episode_900, episode_750, episode_4550, episode_300, episode_600, episode_2550, episode_950, episode_1300, episode_3900</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3671,7 +3569,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_4300, rank_02, top_ep_3350, rank_03, top_ep_2600, rank_04, top_ep_2050, rank_05, top_ep_2250, rank_06, top_ep_2200, rank_07, top_ep_1900, rank_08, top_ep_2400, rank_09, top_ep_1050, rank_10, top_ep_1350</t>
+          <t>rank_01, top_ep_4300, rank_02, top_ep_3350, rank_03, top_ep_2600, rank_04, top_ep_2050, rank_05, top_ep_2250, rank_06, top_ep_2200, rank_07, top_ep_1900, rank_08, top_ep_2400, rank_09, top_ep_1050, rank_10, top_ep_1350, episode_4300, episode_3350, episode_2600, episode_2050, episode_2250, episode_2200, episode_1900, episode_2400, episode_1050, episode_1350</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3716,7 +3614,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_850, rank_02, top_ep_1650, rank_03, top_ep_2250, rank_04, top_ep_1000, rank_05, top_ep_1500, rank_06, top_ep_3650, rank_07, top_ep_2750, rank_08, top_ep_1250, rank_09, top_ep_1750, rank_10, top_ep_3400</t>
+          <t>rank_01, top_ep_850, rank_02, top_ep_1650, rank_03, top_ep_2250, rank_04, top_ep_1000, rank_05, top_ep_1500, rank_06, top_ep_3650, rank_07, top_ep_2750, rank_08, top_ep_1250, rank_09, top_ep_1750, rank_10, top_ep_3400, episode_850, episode_1650, episode_2250, episode_1000, episode_1500, episode_3650, episode_2750, episode_1250, episode_1750, episode_3400</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -3761,7 +3659,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_1600, rank_02, top_ep_4150, rank_03, top_ep_2150, rank_04, top_ep_1450, rank_05, top_ep_2250, rank_06, top_ep_3950, rank_07, top_ep_3450, rank_08, top_ep_2900, rank_09, top_ep_3150, rank_10, top_ep_1650</t>
+          <t>rank_01, top_ep_1600, rank_02, top_ep_4150, rank_03, top_ep_2150, rank_04, top_ep_1450, rank_05, top_ep_2250, rank_06, top_ep_3950, rank_07, top_ep_3450, rank_08, top_ep_2900, rank_09, top_ep_3150, rank_10, top_ep_1650, episode_1600, episode_4150, episode_2150, episode_1450, episode_2250, episode_3950, episode_3450, episode_2900, episode_3150, episode_1650</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3806,7 +3704,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>rank_01, top_ep_3350, rank_02, top_ep_1850, rank_03, top_ep_4850, rank_04, top_ep_2600, rank_05, top_ep_2200, rank_06, top_ep_3800, rank_07, top_ep_4550, rank_08, top_ep_3700, rank_09, top_ep_1250, rank_10, top_ep_2050</t>
+          <t>rank_01, top_ep_3350, rank_02, top_ep_1850, rank_03, top_ep_4850, rank_04, top_ep_2600, rank_05, top_ep_2200, rank_06, top_ep_3800, rank_07, top_ep_4550, rank_08, top_ep_3700, rank_09, top_ep_1250, rank_10, top_ep_2050, episode_3350, episode_1850, episode_4850, episode_2600, episode_2200, episode_3800, episode_4550, episode_3700, episode_1250, episode_2050</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4441,10 +4339,8 @@
       <c r="F2">
         <v>68.23</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G2">
+        <v>105.38666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -4468,10 +4364,8 @@
       <c r="F3">
         <v>64.05</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G3">
+        <v>88.92333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -4495,10 +4389,8 @@
       <c r="F4">
         <v>69.23</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G4">
+        <v>74.05666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -4537,10 +4429,8 @@
       <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>28.003333333333334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4552,10 +4442,8 @@
           <t/>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F6">
+        <v>55.62</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4572,10 +4460,8 @@
       <c r="B7">
         <v>8</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C7">
+        <v>27.496666666666666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4587,10 +4473,8 @@
           <t/>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F7">
+        <v>46.42</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4619,10 +4503,8 @@
       <c r="F8">
         <v>54.67</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8">
+        <v>78.41</v>
       </c>
     </row>
     <row r="9">
@@ -4646,10 +4528,8 @@
       <c r="F9">
         <v>49.37</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G9">
+        <v>61.88</v>
       </c>
     </row>
     <row r="10">
@@ -4673,10 +4553,8 @@
       <c r="F10">
         <v>49.47</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10">
+        <v>54.8</v>
       </c>
     </row>
     <row r="11">
@@ -4700,10 +4578,8 @@
       <c r="F11">
         <v>46.59</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G11">
+        <v>58.193333333333335</v>
       </c>
     </row>
     <row r="12">
@@ -4715,30 +4591,22 @@
       <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C12">
+        <v>28.613333333333333</v>
+      </c>
+      <c r="D12">
+        <v>37.72666666666667</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F12">
+        <v>47.86666666666667</v>
+      </c>
+      <c r="G12">
+        <v>49.33</v>
       </c>
     </row>
     <row r="13">
@@ -4750,10 +4618,8 @@
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C13">
+        <v>27.293333333333333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4765,10 +4631,8 @@
           <t/>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F13">
+        <v>44.70666666666666</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -5024,15 +4888,11 @@
       <c r="F2">
         <v>26.79</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G2">
+        <v>28.003333333333334</v>
+      </c>
+      <c r="H2">
+        <v>27.496666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -5120,15 +4980,11 @@
       <c r="F5">
         <v>69.19</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G5">
+        <v>55.62</v>
+      </c>
+      <c r="H5">
+        <v>46.42</v>
       </c>
     </row>
     <row r="6">
@@ -5140,20 +4996,14 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>105.38666666666667</v>
+      </c>
+      <c r="D6">
+        <v>88.92333333333333</v>
+      </c>
+      <c r="E6">
+        <v>74.05666666666667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -5192,15 +5042,11 @@
       <c r="F7">
         <v>25.11</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G7">
+        <v>28.613333333333333</v>
+      </c>
+      <c r="H7">
+        <v>27.293333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -5224,10 +5070,8 @@
       <c r="F8">
         <v>34.74</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8">
+        <v>37.72666666666667</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5288,15 +5132,11 @@
       <c r="F10">
         <v>46.59</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10">
+        <v>47.86666666666667</v>
+      </c>
+      <c r="H10">
+        <v>44.70666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -5308,30 +5148,20 @@
       <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C11">
+        <v>78.41</v>
+      </c>
+      <c r="D11">
+        <v>61.88</v>
+      </c>
+      <c r="E11">
+        <v>54.8</v>
+      </c>
+      <c r="F11">
+        <v>58.193333333333335</v>
+      </c>
+      <c r="G11">
+        <v>49.33</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5572,10 +5402,8 @@
       <c r="F2">
         <v>270.31</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G2">
+        <v>262.76666666666665</v>
       </c>
     </row>
     <row r="3">
@@ -5599,10 +5427,8 @@
       <c r="F3">
         <v>254.53</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G3">
+        <v>319.6</v>
       </c>
     </row>
     <row r="4">
@@ -5626,10 +5452,8 @@
       <c r="F4">
         <v>238.94</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G4">
+        <v>354.4766666666667</v>
       </c>
     </row>
     <row r="5">
@@ -5668,10 +5492,8 @@
       <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>119.15333333333334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5683,10 +5505,8 @@
           <t/>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F6">
+        <v>341.1933333333333</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5703,10 +5523,8 @@
       <c r="B7">
         <v>8</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C7">
+        <v>134.44333333333333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5718,10 +5536,8 @@
           <t/>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F7">
+        <v>207.50666666666666</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5750,10 +5566,8 @@
       <c r="F8">
         <v>136.46</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8">
+        <v>129.13333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -5777,10 +5591,8 @@
       <c r="F9">
         <v>138.95</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G9">
+        <v>161.1</v>
       </c>
     </row>
     <row r="10">
@@ -5804,10 +5616,8 @@
       <c r="F10">
         <v>140.96</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10">
+        <v>174.38666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -5831,10 +5641,8 @@
       <c r="F11">
         <v>133.19</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G11">
+        <v>203.61</v>
       </c>
     </row>
     <row r="12">
@@ -5846,30 +5654,22 @@
       <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C12">
+        <v>43.14</v>
+      </c>
+      <c r="D12">
+        <v>87.44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F12">
+        <v>174.24</v>
+      </c>
+      <c r="G12">
+        <v>205.52333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -5881,10 +5681,8 @@
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C13">
+        <v>47.29333333333334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5896,10 +5694,8 @@
           <t/>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F13">
+        <v>172.01666666666668</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -6155,15 +5951,11 @@
       <c r="F2">
         <v>96.36</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G2">
+        <v>119.15333333333334</v>
+      </c>
+      <c r="H2">
+        <v>134.44333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -6251,15 +6043,11 @@
       <c r="F5">
         <v>266.95</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G5">
+        <v>341.1933333333333</v>
+      </c>
+      <c r="H5">
+        <v>207.50666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -6271,20 +6059,14 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>262.76666666666665</v>
+      </c>
+      <c r="D6">
+        <v>319.6</v>
+      </c>
+      <c r="E6">
+        <v>354.4766666666667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6323,15 +6105,11 @@
       <c r="F7">
         <v>32.65</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G7">
+        <v>43.14</v>
+      </c>
+      <c r="H7">
+        <v>47.29333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -6355,10 +6133,8 @@
       <c r="F8">
         <v>68.92</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8">
+        <v>87.44</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -6419,15 +6195,11 @@
       <c r="F10">
         <v>133.19</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10">
+        <v>174.24</v>
+      </c>
+      <c r="H10">
+        <v>172.01666666666668</v>
       </c>
     </row>
     <row r="11">
@@ -6439,30 +6211,20 @@
       <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C11">
+        <v>129.13333333333333</v>
+      </c>
+      <c r="D11">
+        <v>161.1</v>
+      </c>
+      <c r="E11">
+        <v>174.38666666666666</v>
+      </c>
+      <c r="F11">
+        <v>203.61</v>
+      </c>
+      <c r="G11">
+        <v>205.52333333333334</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -6703,10 +6465,8 @@
       <c r="F2">
         <v>0.9189719999999998</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G2">
+        <v>0.8853066666666666</v>
       </c>
     </row>
     <row r="3">
@@ -6730,10 +6490,8 @@
       <c r="F3">
         <v>0.9163439999999998</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G3">
+        <v>0.9134626666666668</v>
       </c>
     </row>
     <row r="4">
@@ -6757,10 +6515,8 @@
       <c r="F4">
         <v>0.9292199999999999</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G4">
+        <v>0.9550706666666665</v>
       </c>
     </row>
     <row r="5">
@@ -6799,10 +6555,8 @@
       <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>0.9783186666666666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6814,10 +6568,8 @@
           <t/>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F6">
+        <v>0.966164</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -6834,10 +6586,8 @@
       <c r="B7">
         <v>8</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C7">
+        <v>0.975552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6849,10 +6599,8 @@
           <t/>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F7">
+        <v>0.9791479999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6881,10 +6629,8 @@
       <c r="F8">
         <v>0.9631239999999999</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8">
+        <v>0.9559293333333331</v>
       </c>
     </row>
     <row r="9">
@@ -6908,10 +6654,8 @@
       <c r="F9">
         <v>0.9727400000000002</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G9">
+        <v>0.9769506666666666</v>
       </c>
     </row>
     <row r="10">
@@ -6935,10 +6679,8 @@
       <c r="F10">
         <v>0.9805839999999999</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10">
+        <v>0.9855933333333333</v>
       </c>
     </row>
     <row r="11">
@@ -6962,10 +6704,8 @@
       <c r="F11">
         <v>0.9700720000000002</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G11">
+        <v>0.9791933333333332</v>
       </c>
     </row>
     <row r="12">
@@ -6977,30 +6717,22 @@
       <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C12">
+        <v>0.9898626666666667</v>
+      </c>
+      <c r="D12">
+        <v>0.9834999999999998</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F12">
+        <v>0.9897293333333335</v>
+      </c>
+      <c r="G12">
+        <v>0.9877413333333334</v>
       </c>
     </row>
     <row r="13">
@@ -7012,10 +6744,8 @@
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C13">
+        <v>0.9854226666666667</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7027,10 +6757,8 @@
           <t/>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F13">
+        <v>0.9908079999999999</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -7286,15 +7014,11 @@
       <c r="F2">
         <v>0.9397800000000001</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G2">
+        <v>0.9783186666666666</v>
+      </c>
+      <c r="H2">
+        <v>0.975552</v>
       </c>
     </row>
     <row r="3">
@@ -7382,15 +7106,11 @@
       <c r="F5">
         <v>0.9006839999999999</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G5">
+        <v>0.966164</v>
+      </c>
+      <c r="H5">
+        <v>0.9791479999999999</v>
       </c>
     </row>
     <row r="6">
@@ -7402,20 +7122,14 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C6">
+        <v>0.8853066666666666</v>
+      </c>
+      <c r="D6">
+        <v>0.9134626666666668</v>
+      </c>
+      <c r="E6">
+        <v>0.9550706666666665</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7454,15 +7168,11 @@
       <c r="F7">
         <v>0.9681879999999998</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G7">
+        <v>0.9898626666666667</v>
+      </c>
+      <c r="H7">
+        <v>0.9854226666666667</v>
       </c>
     </row>
     <row r="8">
@@ -7486,10 +7196,8 @@
       <c r="F8">
         <v>0.9775720000000001</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G8">
+        <v>0.9834999999999998</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7550,15 +7258,11 @@
       <c r="F10">
         <v>0.9700720000000002</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G10">
+        <v>0.9897293333333335</v>
+      </c>
+      <c r="H10">
+        <v>0.9908079999999999</v>
       </c>
     </row>
     <row r="11">
@@ -7570,30 +7274,20 @@
       <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="C11">
+        <v>0.9559293333333331</v>
+      </c>
+      <c r="D11">
+        <v>0.9769506666666666</v>
+      </c>
+      <c r="E11">
+        <v>0.9855933333333333</v>
+      </c>
+      <c r="F11">
+        <v>0.9791933333333332</v>
+      </c>
+      <c r="G11">
+        <v>0.9877413333333334</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -7821,7 +7515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>newnet_6_3_compare</t>
+          <t>newnet_6_6_compare</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7830,17 +7524,17 @@
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_3750, top_ep_3750, episode_3800, top_ep_3800, episode_4200, top_ep_4200, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_350, top_ep_350, episode_400, top_ep_400, episode_50, top_ep_50, episode_650, top_ep_650, episode_700, top_ep_700, episode_750, top_ep_750</t>
+          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_1500, top_ep_1500, episode_200, top_ep_200, episode_250, top_ep_250, episode_2950, top_ep_2950, episode_300, top_ep_300, episode_3200, top_ep_3200, episode_3400, top_ep_3400, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600, episode_650, top_ep_650, episode_700, top_ep_700, episode_750, top_ep_750, episode_950, top_ep_950</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7850,14 +7544,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>newnet_6_4_compare</t>
+          <t>newnet_6_7_compare</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7866,17 +7560,17 @@
         </is>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_2050, top_ep_2050, episode_2750, top_ep_2750, episode_800, top_ep_800</t>
+          <t>episode_100, top_ep_100, episode_1150, top_ep_1150, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7886,14 +7580,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>newnet_6_5_compare</t>
+          <t>newnet_6_7_compare</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7902,17 +7596,17 @@
         </is>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1000, top_ep_1000, episode_1050, top_ep_1050, episode_1100, top_ep_1100</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7922,14 +7616,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>newnet_6_6_compare</t>
+          <t>newnet_6_7_compare</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7938,17 +7632,17 @@
         </is>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_1500, top_ep_1500, episode_200, top_ep_200, episode_250, top_ep_250, episode_2950, top_ep_2950, episode_300, top_ep_300, episode_3200, top_ep_3200, episode_3400, top_ep_3400, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600, episode_650, top_ep_650, episode_700, top_ep_700, episode_750, top_ep_750, episode_950, top_ep_950</t>
+          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_1700, top_ep_1700, episode_200, top_ep_200, episode_250, top_ep_250, episode_400, top_ep_400, episode_50, top_ep_50, episode_550, top_ep_550, episode_650, top_ep_650, episode_700, top_ep_700, episode_750, top_ep_750, episode_800, top_ep_800, episode_900, top_ep_900</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7958,14 +7652,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7974,17 +7668,17 @@
         </is>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_2050, top_ep_2050, episode_4050, top_ep_4050, episode_700, top_ep_700, episode_100, top_ep_100, episode_1050, top_ep_1050, episode_1250, top_ep_1250, episode_1300, top_ep_1300, episode_1350, top_ep_1350, episode_150, top_ep_150, episode_1500, top_ep_1500, episode_1800, top_ep_1800, episode_250, top_ep_250, episode_300, top_ep_300, episode_400, top_ep_400, episode_50, top_ep_50, episode_550, top_ep_550, episode_950, top_ep_950, episode_1100, top_ep_1100, episode_200, top_ep_200, episode_450, top_ep_450, episode_500, top_ep_500, episode_600, top_ep_600, episode_650, top_ep_650, episode_800, top_ep_800, episode_900, top_ep_900</t>
+          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_400, top_ep_400, episode_50, top_ep_50, episode_650, top_ep_650, episode_700, top_ep_700</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7994,14 +7688,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8010,17 +7704,17 @@
         </is>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>episode_100, top_ep_100, episode_1150, top_ep_1150, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8030,14 +7724,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8046,17 +7740,17 @@
         </is>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_50, top_ep_50, episode_900, top_ep_900</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8066,7 +7760,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8078,21 +7772,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_nopf</t>
         </is>
       </c>
       <c r="C9">
         <v>7</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_2450, top_ep_2450, episode_3250, top_ep_3250, episode_4150, top_ep_4150, episode_100, top_ep_100, episode_1050, top_ep_1050, episode_150, top_ep_150, episode_1900, top_ep_1900, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_50, top_ep_50, episode_500, top_ep_500, episode_700, top_ep_700, episode_750, top_ep_750, episode_1000, top_ep_1000, episode_950, top_ep_950</t>
+          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8102,33 +7796,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_nopf</t>
         </is>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_1700, top_ep_1700, episode_200, top_ep_200, episode_250, top_ep_250, episode_400, top_ep_400, episode_50, top_ep_50, episode_550, top_ep_550, episode_650, top_ep_650, episode_700, top_ep_700, episode_750, top_ep_750, episode_800, top_ep_800, episode_900, top_ep_900</t>
+          <t>episode_4000, top_ep_4000, episode_100, top_ep_100, episode_1000, top_ep_1000, episode_1050, top_ep_1050, episode_1100, top_ep_1100, episode_1300, top_ep_1300, episode_1350, top_ep_1350, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600, episode_650, top_ep_650, episode_700, top_ep_700</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8138,7 +7832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8150,21 +7844,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_nopf</t>
         </is>
       </c>
       <c r="C11">
         <v>8</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1250, top_ep_1250, episode_1350, top_ep_1350, episode_3150, top_ep_3150, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_650, top_ep_650, episode_750, top_ep_750</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8174,7 +7868,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8186,21 +7880,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_nopf</t>
         </is>
       </c>
       <c r="C12">
         <v>8</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_400, top_ep_400, episode_50, top_ep_50, episode_650, top_ep_650, episode_700, top_ep_700</t>
+          <t>episode_4000, top_ep_4000, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_2300, top_ep_2300, episode_250, top_ep_250, episode_2850, top_ep_2850, episode_300, top_ep_300, episode_3400, top_ep_3400, episode_350, top_ep_350, episode_3500, top_ep_3500, episode_4250, top_ep_4250, episode_4300, top_ep_4300, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8210,26 +7904,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>newnet_6_8_compare</t>
+          <t>newnet_6_3_compare</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -8246,33 +7940,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>newnet_6_8_compare</t>
+          <t>newnet_6_4_compare</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_150, top_ep_150, episode_1800, top_ep_1800, episode_1900, top_ep_1900, episode_100, top_ep_100, episode_1050, top_ep_1050, episode_200, top_ep_200, episode_250, top_ep_250, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_650, top_ep_650, episode_750, top_ep_750, episode_300, top_ep_300, episode_550, top_ep_550, episode_850, top_ep_850</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8282,33 +7976,33 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>newnet_6_8_compare</t>
+          <t>newnet_6_5_compare</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>iddpg</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_50, top_ep_50, episode_900, top_ep_900</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8318,33 +8012,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>newnet_6_3_compare</t>
+          <t>newnet_6_6_compare</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1250, top_ep_1250, episode_1650, top_ep_1650, episode_2850, top_ep_2850, episode_100, top_ep_100, episode_1050, top_ep_1050, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_2750, top_ep_2750, episode_2800, top_ep_2800, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_550, top_ep_550, episode_650, top_ep_650, episode_700, top_ep_700, episode_750, top_ep_750, episode_800, top_ep_800, episode_850, top_ep_850, episode_900, top_ep_900</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8354,33 +8048,33 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>newnet_6_4_compare</t>
+          <t>newnet_6_7_compare</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1050, top_ep_1050, episode_1300, top_ep_1300, episode_1450, top_ep_1450, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600, episode_700, top_ep_700</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8390,33 +8084,33 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>newnet_6_5_compare</t>
+          <t>newnet_6_7_compare</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1750, top_ep_1750, episode_4500, top_ep_4500, episode_4600, top_ep_4600</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8426,33 +8120,33 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>newnet_6_6_compare</t>
+          <t>newnet_6_7_compare</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1400, top_ep_1400, episode_1800, top_ep_1800, episode_900, top_ep_900</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8462,7 +8156,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8474,21 +8168,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C20">
         <v>7</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1000, top_ep_1000, episode_1100, top_ep_1100, episode_1850, top_ep_1850, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_650, top_ep_650, episode_800, top_ep_800, episode_850, top_ep_850, episode_950, top_ep_950</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8498,7 +8192,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8510,21 +8204,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C21">
         <v>7</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1000, top_ep_1000, episode_650, top_ep_650, episode_900, top_ep_900</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8534,33 +8228,33 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8570,33 +8264,33 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_850, top_ep_850, episode_900, top_ep_900, episode_950, top_ep_950, episode_100, top_ep_100, episode_1000, top_ep_1000, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600, episode_650, top_ep_650, episode_700, top_ep_700, episode_800, top_ep_800, episode_750, top_ep_750</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8606,33 +8300,33 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>newnet_6_7_compare</t>
+          <t>newnet_6_8_compare</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1250, top_ep_1250, episode_500, top_ep_500, episode_650, top_ep_650</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8642,7 +8336,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8654,21 +8348,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C25">
         <v>8</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_1200, top_ep_1200, episode_3100, top_ep_3100, episode_550, top_ep_550, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_50, top_ep_50, episode_700, top_ep_700, episode_750, top_ep_750, episode_800, top_ep_800, episode_500, top_ep_500, episode_650, top_ep_650, episode_900, top_ep_900</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8678,7 +8372,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
@@ -8690,21 +8384,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>maddpg_nopf</t>
+          <t>maddpg_our_method</t>
         </is>
       </c>
       <c r="C26">
         <v>8</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>episode_4000, top_ep_4000, episode_100, top_ep_100, episode_1000, top_ep_1000, episode_1050, top_ep_1050, episode_1100, top_ep_1100, episode_1300, top_ep_1300, episode_1350, top_ep_1350, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_350, top_ep_350, episode_400, top_ep_400, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600, episode_650, top_ep_650, episode_700, top_ep_700</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8714,619 +8408,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>maddpg_nopf</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>8</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>maddpg_nopf</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>8</v>
-      </c>
-      <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="E28">
-        <v>34</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>episode_4000, top_ep_4000, episode_1250, top_ep_1250, episode_2400, top_ep_2400, episode_3100, top_ep_3100, episode_100, top_ep_100, episode_1050, top_ep_1050, episode_1100, top_ep_1100, episode_150, top_ep_150, episode_200, top_ep_200, episode_250, top_ep_250, episode_300, top_ep_300, episode_50, top_ep_50, episode_550, top_ep_550, episode_650, top_ep_650, episode_800, top_ep_800, episode_900, top_ep_900, episode_1000, top_ep_1000, episode_350, top_ep_350, episode_450, top_ep_450, episode_500, top_ep_500, episode_600, top_ep_600, episode_850, top_ep_850</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>maddpg_nopf</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>8</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29">
-        <v>19</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>episode_4000, top_ep_4000, episode_100, top_ep_100, episode_150, top_ep_150, episode_200, top_ep_200, episode_2300, top_ep_2300, episode_250, top_ep_250, episode_2850, top_ep_2850, episode_300, top_ep_300, episode_3400, top_ep_3400, episode_350, top_ep_350, episode_3500, top_ep_3500, episode_4250, top_ep_4250, episode_4300, top_ep_4300, episode_450, top_ep_450, episode_50, top_ep_50, episode_500, top_ep_500, episode_550, top_ep_550, episode_600, top_ep_600</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>newnet_6_3_compare</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30">
-        <v>5</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>newnet_6_4_compare</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31">
-        <v>5</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>newnet_6_5_compare</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>5</v>
-      </c>
-      <c r="D32">
-        <v>5</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>newnet_6_6_compare</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>newnet_6_7_compare</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>7</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>newnet_6_7_compare</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>7</v>
-      </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>newnet_6_7_compare</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>7</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>newnet_6_7_compare</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>7</v>
-      </c>
-      <c r="D37">
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>newnet_6_7_compare</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>7</v>
-      </c>
-      <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>8</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>8</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>8</v>
-      </c>
-      <c r="D41">
-        <v>3</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>8</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>newnet_6_8_compare</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>maddpg_our_method</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>8</v>
-      </c>
-      <c r="D43">
-        <v>5</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>no_collect_models_candidate_key_in_metrics_summary</t>
+          <t>metrics_summary_missing</t>
         </is>
       </c>
     </row>
